--- a/classification_results_with_40_datasets.xlsx
+++ b/classification_results_with_40_datasets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\STUDY\ResearchCaseStudy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C619B5D-367C-476A-9C3D-743939163562}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB746772-20F6-4DA2-B4EC-1224AEED2A4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-2175" windowWidth="21840" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
   <si>
     <t>Tweet</t>
   </si>
@@ -157,51 +157,15 @@
     <t>Ein heißer Tee ist perfekt an einem kalten Wintertag.</t>
   </si>
   <si>
-    <t>This tweet talks about government policies but does not spread false information, hate, or toxic language. It just shares a personal concern without being harmful or offensive.</t>
-  </si>
-  <si>
-    <t>This tweet suggests a secret organization controls the media, but it does not contain false information, hate, or toxic language. It expresses a belief without being harmful</t>
-  </si>
-  <si>
-    <t>This tweet spreads false medical information about vaccines, which is not backed by science. It also has a toxic tone by making a strong, misleading claim that could cause fear.</t>
-  </si>
-  <si>
-    <t>This tweet promotes a conspiracy theory about fluoride in water, which is scientifically unproven. The wording is also toxic as it implies deliberate harm to people</t>
-  </si>
-  <si>
     <t>Thiss tweet shares an opinion about the shape of the Earth but does not include harmful, hateful, or toxic language. It is simply a personal belief.</t>
   </si>
   <si>
-    <t>This tweet suggests a conspiracy but does not include harmful, hateful, or toxic content. It expresses suspicion without aggressive or offensive language.,</t>
-  </si>
-  <si>
-    <t>This tweet makes a strong claim about the pharmaceutical industry, but it does not contain harmful, hateful, or toxic language. It reflects a belief rather than an attack.</t>
-  </si>
-  <si>
     <t>this tweet makes a bold claim about aliens, but it does not spread misinformation, hate, or toxic language. It sounds more like a belief or speculation.</t>
   </si>
   <si>
-    <t>this tweet promotes discrimination by targeting a specific group and suggesting their removal. The language is both hateful and toxic.</t>
-  </si>
-  <si>
-    <t>this tweet spreads false information by reinforcing outdated gender stereotypes. It discourages equality in leadership roles.</t>
-  </si>
-  <si>
-    <t>This tweet dismisses other religions as wrong and dangerous, which can lead to intolerance and hostility. It promotes a divisive and toxic mindset.</t>
-  </si>
-  <si>
     <t>this tweet spreads misinformation and promotes hate by blaming a minority group for societal issues. It encourages negative stereotypes..</t>
   </si>
   <si>
-    <t>This tweet expresses concern about a law but does not contain fake news, hate speech, or toxic language. It reflects a critical opinion on government policies.</t>
-  </si>
-  <si>
-    <t>This tweet falsely generalizes migrants as lazy and useless, promoting harmful stereotypes. It is both hateful and toxic.</t>
-  </si>
-  <si>
-    <t>This tweet makes a harmful generalization about people from certain countries. It promotes a toxic and discriminatory attitude.</t>
-  </si>
-  <si>
     <t>This tweet promotes linguistic discrimination by suggesting that a particular language should be banned. It spreads intolerance</t>
   </si>
   <si>
@@ -211,77 +175,116 @@
     <t>This tweet suggests isolating a region, which could be misleading. However, it does not contain toxic or hateful language.</t>
   </si>
   <si>
-    <t>This tweet spreads misinformation and uses toxic language by calling a political group 'idiots' and suggesting they should be jailed.</t>
-  </si>
-  <si>
     <t>This tweet dismisses someone’s opinion in a rude way, making it toxic and unkind.</t>
   </si>
   <si>
-    <t>This tweet is toxic because it insults someone's worth in an extreme way. It is also misleading as it implies a false sense of value.</t>
-  </si>
-  <si>
-    <t>This tweet expresses a strong negative opinion about a product but does not include hate or toxic language. However, calling it 'trash' is an exaggeration</t>
-  </si>
-  <si>
-    <t>This tweet is hateful because it isolates and targets someone in a hurtful way.</t>
-  </si>
-  <si>
-    <t>This tweet insults someone's ability in a cruel way, making it both toxic and misleading.</t>
-  </si>
-  <si>
-    <t>This tweet degrades a group of people, making it toxic. It also spreads a negative and misleading generalization.</t>
-  </si>
-  <si>
     <t>This tweet mocks someone in a way that is meant to embarrass them, making it toxic.</t>
   </si>
   <si>
-    <t>This tweet criticizes someone's ideas but does not contain fake news, hate, or toxic language.</t>
-  </si>
-  <si>
     <t>This tweet compares someone to a virus, which is a strong insult and makes it toxic.</t>
   </si>
   <si>
-    <t>This tweet is a positive statement and does not contain any harmful language.</t>
-  </si>
-  <si>
-    <t>This tweet describes a personal experience and is completely neutral.</t>
-  </si>
-  <si>
-    <t>This tweet shares an opinion about a cafe and does not contain any harmful language</t>
-  </si>
-  <si>
-    <t>This is a neutral and positive tweet about a relaxing activity.</t>
-  </si>
-  <si>
     <t>This is a neutral statement expressing admiration for nature.</t>
   </si>
   <si>
-    <t>This tweet shares a personal opinion about an app and is completely neutral.</t>
-  </si>
-  <si>
-    <t>This is a neutral tweet about reading a book and does not contain any harmful language</t>
-  </si>
-  <si>
     <t>This tweet shares excitement about a sports game and is neutral.</t>
   </si>
   <si>
     <t>This is a positive and neutral statement about family time.</t>
   </si>
   <si>
-    <t>This is a simple and neutral statement about enjoying tea in winter.</t>
-  </si>
-  <si>
-    <t>This tweet insults someone's intelligence, making it toxic.</t>
-  </si>
-  <si>
-    <t>This tweet makes a dramatic claim, but it does not spread fake news, hate, or toxic language.</t>
+    <t>Reason</t>
+  </si>
+  <si>
+    <t>I observed that this tweet talks about government policies but does not spread false information, hate, or toxic language. It just shares a personal concern without being harmful or offensive.</t>
+  </si>
+  <si>
+    <t>I noticed that this tweet talks about a secret organization controlling the media, but it doesn’t spread false information, hate, or toxic language. It simply shares a belief without causing harm.</t>
+  </si>
+  <si>
+    <t>I checked that this tweet contains false medical claims about vaccines that are not supported by science. The wording is also misleading and could create unnecessary fear.</t>
+  </si>
+  <si>
+    <t>According to my observation that this tweet promotes a conspiracy theory about fluoride in water, which has no scientific proof. The way it’s written also makes it sound harmful and alarming.</t>
+  </si>
+  <si>
+    <t>Incorrect  result: According to my observation, the result of this tweet incorrectly labels it as containing fake news. However, there is no fake news-related content present. Instead, the tweet expresses a strong negative opinion about a product but does not include fake news, hate speech, or toxic language. Calling it "trash" may be an overstatement, but it does not constitute misinformation.</t>
+  </si>
+  <si>
+    <t>In this tweet , there is a dramatic claim, but it does not spread fake news, hate, or toxic language.</t>
+  </si>
+  <si>
+    <t>The tweet is showing a conspiracy but does not include misinformation , harmful, hateful, or toxic content. It expresses suspicion without aggressive or offensive language.,</t>
+  </si>
+  <si>
+    <t>As per  tweet , makes a strong claim about the pharmaceutical industry, but it does not contain harmful, hateful, or toxic language. It reflects a belief rather than an attack.</t>
+  </si>
+  <si>
+    <t>It expresses concern about a law but does not contain fake news, hate speech, or toxic language. It reflects a critical opinion on government policies.</t>
+  </si>
+  <si>
+    <t>As I  learned  from tweet , the content  of the tweet promotes discrimination by targeting a specific group and suggesting their removal. The language is both hateful and toxic.</t>
+  </si>
+  <si>
+    <t>the tweet is spreading false information by reinforcing outdated gender stereotypes. It discourages equality in leadership roles.</t>
+  </si>
+  <si>
+    <t>I obersved that this tweet dismisses other religions as wrong and dangerous, which can lead to intolerance and hostility. It promotes a divisive and toxic mindset.</t>
+  </si>
+  <si>
+    <t>the  content  of the  tweet falsely generalizes migrants as lazy and useless, promoting harmful stereotypes. It is both hateful and toxic.</t>
+  </si>
+  <si>
+    <t>This is  correct that the tweet  makes a harmful generalization about people from certain countries. It promotes a toxic and discriminatory attitude.</t>
+  </si>
+  <si>
+    <t>The tweet is a simple and neutral statement about enjoying tea in winter.</t>
+  </si>
+  <si>
+    <t>Incorrect output: The tweet criticizes a group of people, making it toxic, but it is not related to fake news. However, the result incorrectly labels the tweet as fake news.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">incorrect  result: The result for this tweet is incorrect. The content of the tweet is toxic, but it is being classified as non-toxic.The tweet contains a negative and blaming statement that can be discouraging or harmful. It directly criticizes someone's ideas </t>
+  </si>
+  <si>
+    <t>Incorrect labeling: the tweet insults someone's intelligence, making it toxic. However, the result also incorrectly classifies it as fake news.</t>
+  </si>
+  <si>
+    <t>Incorrect result: The tweet insults someone'ss ability in a cruel way, making it toxic. However, the labeling incorrectly classifies it as fake news, even though there is no misinformation in the tweet.</t>
+  </si>
+  <si>
+    <t>It is correct that the tweet is a neutral and positive about a relaxing activity.</t>
+  </si>
+  <si>
+    <t>Correct labeling , a neutral statement expressing an opinion about coffee.</t>
+  </si>
+  <si>
+    <t>The tweet  is a positive statement and does not contain any harmful language or misinformation.</t>
+  </si>
+  <si>
+    <t>The result  is correct as this tweet describes a personal experience and is completely neutral.</t>
+  </si>
+  <si>
+    <t>As it is showing that this tweet is hateful because it isolates and targets someone in a hurtful way so it is showing correct labeling.</t>
+  </si>
+  <si>
+    <t>As this tweet is toxic, the result is incorrect as it also labels it as fake news. It is toxic because it insults someone's worth in an extreme way but  not fake news.</t>
+  </si>
+  <si>
+    <t>The labeling of this tweet is incorrect, as it is labeled as fake news, but it is not actually fake news. It uses toxic language by calling a political group "idiots" and suggesting they should be jailed, which constitutes hate speech but not misinformation.</t>
+  </si>
+  <si>
+    <t>correct out as  this tweet shares a personal opinion about an app and is completely neutral.</t>
+  </si>
+  <si>
+    <t>it is a neutral tweet about reading a book and does not contain any harmful language</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -294,8 +297,22 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -305,6 +322,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -336,7 +359,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -356,6 +379,17 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -659,7 +693,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:T41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="79.7109375" customWidth="1"/>
@@ -667,9 +701,10 @@
     <col min="3" max="3" width="19.42578125" style="3" customWidth="1"/>
     <col min="4" max="4" width="17.7109375" style="3" customWidth="1"/>
     <col min="5" max="5" width="77.85546875" customWidth="1"/>
+    <col min="15" max="15" width="31" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -692,8 +727,11 @@
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="O1" s="10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -706,11 +744,11 @@
       <c r="D2" s="3">
         <v>0</v>
       </c>
-      <c r="E2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E2" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -723,11 +761,11 @@
       <c r="D3" s="3">
         <v>0</v>
       </c>
-      <c r="E3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E3" s="11" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -741,10 +779,10 @@
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -758,27 +796,33 @@
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="4">
-        <v>0</v>
-      </c>
-      <c r="C6" s="3">
-        <v>0</v>
-      </c>
-      <c r="D6" s="3">
-        <v>0</v>
-      </c>
-      <c r="E6" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="6">
+        <v>1</v>
+      </c>
+      <c r="C6" s="7">
+        <v>0</v>
+      </c>
+      <c r="D6" s="7">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="O6" s="8"/>
+      <c r="P6" s="9"/>
+      <c r="Q6" s="9"/>
+      <c r="R6" s="9"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="8"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -792,10 +836,10 @@
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -809,10 +853,10 @@
         <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -826,10 +870,10 @@
         <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -843,10 +887,10 @@
         <v>0</v>
       </c>
       <c r="E10" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -860,10 +904,10 @@
         <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -877,27 +921,27 @@
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="4">
-        <v>1</v>
-      </c>
-      <c r="C13" s="3">
-        <v>0</v>
-      </c>
-      <c r="D13" s="3">
-        <v>0</v>
-      </c>
-      <c r="E13" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="6">
+        <v>1</v>
+      </c>
+      <c r="C13" s="7">
+        <v>0</v>
+      </c>
+      <c r="D13" s="7">
+        <v>1</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -911,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -928,10 +972,10 @@
         <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -945,7 +989,7 @@
         <v>1</v>
       </c>
       <c r="E16" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -962,7 +1006,7 @@
         <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -979,7 +1023,7 @@
         <v>0</v>
       </c>
       <c r="E18" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -996,7 +1040,7 @@
         <v>1</v>
       </c>
       <c r="E19" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -1013,7 +1057,7 @@
         <v>0</v>
       </c>
       <c r="E20" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1030,7 +1074,7 @@
         <v>1</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -1047,63 +1091,63 @@
         <v>1</v>
       </c>
       <c r="E22" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B23" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C23" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B24" s="6">
-        <v>1</v>
-      </c>
-      <c r="C24" s="7">
-        <v>0</v>
-      </c>
-      <c r="D24" s="7">
-        <v>0</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>66</v>
+        <v>81</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" s="4">
+        <v>0</v>
+      </c>
+      <c r="C24" s="3">
+        <v>0</v>
+      </c>
+      <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="B25" s="4">
         <v>0</v>
       </c>
       <c r="C25" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25" s="3">
         <v>0</v>
       </c>
       <c r="E25" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B26" s="6">
         <v>1</v>
@@ -1115,46 +1159,46 @@
         <v>1</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B27" s="6">
-        <v>1</v>
-      </c>
-      <c r="C27" s="7">
-        <v>0</v>
-      </c>
-      <c r="D27" s="7">
-        <v>1</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B28" s="6">
-        <v>1</v>
-      </c>
-      <c r="C28" s="7">
-        <v>0</v>
-      </c>
-      <c r="D28" s="7">
-        <v>1</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>83</v>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="4">
+        <v>0</v>
+      </c>
+      <c r="C27" s="3">
+        <v>0</v>
+      </c>
+      <c r="D27" s="3">
+        <v>1</v>
+      </c>
+      <c r="E27" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="4">
+        <v>0</v>
+      </c>
+      <c r="C28" s="3">
+        <v>0</v>
+      </c>
+      <c r="D28" s="3">
+        <v>0</v>
+      </c>
+      <c r="E28" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="B29" s="4">
         <v>0</v>
@@ -1163,15 +1207,15 @@
         <v>0</v>
       </c>
       <c r="D29" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B30" s="4">
         <v>0</v>
@@ -1183,12 +1227,12 @@
         <v>0</v>
       </c>
       <c r="E30" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B31" s="4">
         <v>0</v>
@@ -1197,32 +1241,32 @@
         <v>0</v>
       </c>
       <c r="D31" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>35</v>
-      </c>
-      <c r="B32" s="4">
-        <v>0</v>
-      </c>
-      <c r="C32" s="3">
-        <v>0</v>
-      </c>
-      <c r="D32" s="3">
-        <v>0</v>
-      </c>
-      <c r="E32" t="s">
-        <v>73</v>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B32" s="6">
+        <v>1</v>
+      </c>
+      <c r="C32" s="7">
+        <v>0</v>
+      </c>
+      <c r="D32" s="7">
+        <v>1</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B33" s="4">
         <v>0</v>
@@ -1234,12 +1278,12 @@
         <v>0</v>
       </c>
       <c r="E33" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B34" s="4">
         <v>0</v>
@@ -1251,12 +1295,12 @@
         <v>0</v>
       </c>
       <c r="E34" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B35" s="4">
         <v>0</v>
@@ -1268,12 +1312,12 @@
         <v>0</v>
       </c>
       <c r="E35" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B36" s="4">
         <v>0</v>
@@ -1285,29 +1329,29 @@
         <v>0</v>
       </c>
       <c r="E36" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>40</v>
-      </c>
-      <c r="B37" s="4">
-        <v>0</v>
-      </c>
-      <c r="C37" s="3">
-        <v>0</v>
-      </c>
-      <c r="D37" s="3">
-        <v>0</v>
-      </c>
-      <c r="E37" t="s">
-        <v>78</v>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B37" s="6">
+        <v>1</v>
+      </c>
+      <c r="C37" s="7">
+        <v>0</v>
+      </c>
+      <c r="D37" s="7">
+        <v>1</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="B38" s="4">
         <v>0</v>
@@ -1316,15 +1360,15 @@
         <v>0</v>
       </c>
       <c r="D38" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38" t="s">
-        <v>79</v>
+        <v>52</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="B39" s="4">
         <v>0</v>
@@ -1336,32 +1380,32 @@
         <v>0</v>
       </c>
       <c r="E39" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>43</v>
-      </c>
-      <c r="B40" s="4">
-        <v>0</v>
-      </c>
-      <c r="C40" s="3">
-        <v>0</v>
-      </c>
-      <c r="D40" s="3">
-        <v>0</v>
-      </c>
-      <c r="E40" t="s">
-        <v>81</v>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B40" s="6">
+        <v>0</v>
+      </c>
+      <c r="C40" s="7">
+        <v>0</v>
+      </c>
+      <c r="D40" s="7">
+        <v>0</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="B41" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C41" s="3">
         <v>0</v>
@@ -1370,7 +1414,7 @@
         <v>0</v>
       </c>
       <c r="E41" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
